--- a/tasks/finalpool/music-analysis/groundtruth_workspace/music_analysis_result.xlsx
+++ b/tasks/finalpool/music-analysis/groundtruth_workspace/music_analysis_result.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1940" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1941" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1942" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1943" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="1944" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="1945" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="1946" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="1947" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="1948" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="1949" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1940" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1941" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1942" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1943" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1944" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1945" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1946" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1947" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1948" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1949" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1646,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3910,16 +3910,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Here Comes Santa Claus</t>
+          <t>Gloria</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gene Autry</t>
+          <t>Mills Brothers</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -3933,12 +3933,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Homecoming Waltz</t>
+          <t>Here Comes Santa Claus</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Guy Lombardo &amp; His Royal Canadians</t>
+          <t>Gene Autry</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -3956,16 +3956,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Hop Scotch Polka</t>
+          <t>Homecoming Waltz</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Art Mooney &amp; His Orchestra</t>
+          <t>Guy Lombardo &amp; His Royal Canadians</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -3984,11 +3984,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Guy Lombardo &amp; His Orchestra</t>
+          <t>Art Mooney &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4002,16 +4002,16 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Hucklebuck</t>
+          <t>Hop Scotch Polka</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Frank Sinatra</t>
+          <t>Guy Lombardo &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -4030,11 +4030,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tommy Dorsey with Charlie Shavers</t>
+          <t>Frank Sinatra</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4048,16 +4048,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>I Can Dream, Can't I?</t>
+          <t>Hucklebuck</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tex Beneke and His Orchestra</t>
+          <t>Tommy Dorsey with Charlie Shavers</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4071,16 +4071,16 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>I Don't See Me In Your Eyes Anymore</t>
+          <t>I Can Dream, Can't I?</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Gordon Jenkins with The Stardusters</t>
+          <t>Tex Beneke and His Orchestra</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Gordon Jenkins with The Stardusters</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -4117,16 +4117,16 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>I Love You So Much It Hurts</t>
+          <t>I Don't See Me In Your Eyes Anymore</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jimmy Wakely and His Cowboy Band</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -4145,11 +4145,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mills Brothers</t>
+          <t>Jimmy Wakely and His Cowboy Band</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -4163,16 +4163,16 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>I Never See Maggie Alone</t>
+          <t>I Love You So Much It Hurts</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Art Mooney &amp; His Orchestra</t>
+          <t>Mills Brothers</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -4191,11 +4191,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kenny Roberts</t>
+          <t>Art Mooney &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -4209,16 +4209,16 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>I Wanna Go Home</t>
+          <t>I Never See Maggie Alone</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Perry Como with the Fontane Sisters</t>
+          <t>Kenny Roberts</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -4232,16 +4232,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>I Yust Go Nuts at Christmas</t>
+          <t>I Wanna Go Home</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Yogi Yorgesson</t>
+          <t>Perry Como with the Fontane Sisters</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -4255,16 +4255,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>I'll Never Slip Around Again</t>
+          <t>I Yust Go Nuts at Christmas</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jimmy Wakely and Margaret Whiting</t>
+          <t>Yogi Yorgesson</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -4278,16 +4278,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>I've Got My Love to Keep Me Warm</t>
+          <t>I'll Never Slip Around Again</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Les Brown</t>
+          <t>Jimmy Wakely and Margaret Whiting</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -4306,11 +4306,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mills Brothers</t>
+          <t>Les Brown</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -4324,16 +4324,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>I've Got a Lovely Bunch of Coconuts</t>
+          <t>I've Got My Love to Keep Me Warm</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Freddie Martin &amp; His Orchestra</t>
+          <t>Mills Brothers</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4347,16 +4347,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jealous Heart</t>
+          <t>I've Got a Lovely Bunch of Coconuts</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Al Morgan</t>
+          <t>Freddie Martin &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -4375,11 +4375,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bill Lawrence</t>
+          <t>Al Morgan</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -4398,11 +4398,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jack Owens</t>
+          <t>Bill Lawrence</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -4421,11 +4421,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jan Garber and His Orchestra</t>
+          <t>Jack Owens</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -4439,16 +4439,16 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Johnson Rag</t>
+          <t>Jealous Heart</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Jack Teter Trio</t>
+          <t>Jan Garber and His Orchestra</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -4462,16 +4462,16 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Just One Way to Say I Love You</t>
+          <t>Johnson Rag</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Jack Teter Trio</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -4485,12 +4485,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Lady of Spain</t>
+          <t>Just One Way to Say I Love You</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ray Noble and his Orchestra</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -4508,16 +4508,16 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Lavender Blue</t>
+          <t>Lady of Spain</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Ray Noble and his Orchestra</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -4536,11 +4536,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Jack Smith with The Clark Sisters</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -4559,11 +4559,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sammy Kaye with Don Cornell &amp; The Kaydets</t>
+          <t>Jack Smith with The Clark Sisters</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -4577,16 +4577,16 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Let's Take an Old-Fashioned Walk</t>
+          <t>Lavender Blue</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Sammy Kaye with Don Cornell &amp; The Kaydets</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -4600,16 +4600,16 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maybe It's Because</t>
+          <t>Let's Take an Old-Fashioned Walk</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Eddy Howard &amp; his Orchestra</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -4628,11 +4628,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Gordon Jenkins &amp; His Orchestra with Dick Haymes</t>
+          <t>Eddy Howard &amp; his Orchestra</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -4646,16 +4646,16 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Merry Christmas Polka</t>
+          <t>Maybe It's Because</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Guy Lombardo with the Andrews Sisters</t>
+          <t>Gordon Jenkins &amp; His Orchestra with Dick Haymes</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -4669,12 +4669,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Merry-Go-Round Waltz</t>
+          <t>Merry Christmas Polka</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Art Mooney and His Orchestra</t>
+          <t>Guy Lombardo with the Andrews Sisters</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -4697,11 +4697,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Guy Lombardo</t>
+          <t>Art Mooney and His Orchestra</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -4715,16 +4715,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Mule Train</t>
+          <t>Merry-Go-Round Waltz</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Guy Lombardo</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -4743,11 +4743,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tennessee Ernie Ford</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -4766,11 +4766,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Vaughn Monroe &amp; His Orchestra</t>
+          <t>Tennessee Ernie Ford</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -4784,16 +4784,16 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>My Bolero</t>
+          <t>Mule Train</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vic Damone</t>
+          <t>Vaughn Monroe &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -4807,16 +4807,16 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>My Darling, My Darling</t>
+          <t>My Bolero</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Doris Day with Buddy Clark</t>
+          <t>Vic Damone</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -4835,11 +4835,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Jo Stafford &amp; Gordon MacRae</t>
+          <t>Doris Day with Buddy Clark</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Need You</t>
+          <t>My Darling, My Darling</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -4876,16 +4876,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Now That I Need You</t>
+          <t>Need You</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Doris Day with The Mellomen</t>
+          <t>Jo Stafford &amp; Gordon MacRae</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -4904,11 +4904,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frankie Laine with Carl Fischer's Orchestra </t>
+          <t>Doris Day with The Mellomen</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -4922,16 +4922,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Now, Now, Now is the Time</t>
+          <t>Now That I Need You</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Russ Morgan and His Orchestra</t>
+          <t xml:space="preserve">Frankie Laine with Carl Fischer's Orchestra </t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -4945,12 +4945,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>On A Slow Boat To China</t>
+          <t>Now, Now, Now is the Time</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Art Lund</t>
+          <t>Russ Morgan and His Orchestra</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -4973,11 +4973,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Benny Goodman with Al Hendrickson</t>
+          <t>Art Lund</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -4996,11 +4996,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Eddy Howard</t>
+          <t>Benny Goodman with Al Hendrickson</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -5019,11 +5019,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Freddy Martin with Glenn Hughes</t>
+          <t>Eddy Howard</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -5037,12 +5037,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Once In Love With Amy</t>
+          <t>On A Slow Boat To China</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ray Bolger</t>
+          <t>Freddy Martin with Glenn Hughes</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -5060,16 +5060,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>One Kiss Too Many</t>
+          <t>Once In Love With Amy</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Eddy Arnold and His Tennessee Plowboys</t>
+          <t>Ray Bolger</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -5083,16 +5083,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Powder Your Face With Sunshine</t>
+          <t>One Kiss Too Many</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sammy Kaye with The Kaydets</t>
+          <t>Eddy Arnold and His Tennessee Plowboys</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -5106,16 +5106,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Red Roses For A Blue Lady</t>
+          <t>Powder Your Face With Sunshine</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Guy Lombardo with Don Rodney</t>
+          <t>Sammy Kaye with The Kaydets</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -5134,11 +5134,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Vaughn Monroe</t>
+          <t>Guy Lombardo with Don Rodney</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -5152,16 +5152,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Riders In The Sky</t>
+          <t>Red Roses For A Blue Lady</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Vaughn Monroe</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -5180,11 +5180,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Burl Ives</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -5198,16 +5198,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Room Full of Roses</t>
+          <t>Riders In The Sky</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dick Haymes</t>
+          <t>Burl Ives</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -5226,11 +5226,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Eddy Howard &amp; his Orchestra</t>
+          <t>Dick Haymes</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -5244,16 +5244,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Saturday Night Fish Fry (Parts I and II)</t>
+          <t>Room Full of Roses</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Louis Jordan &amp; His Tympany Five</t>
+          <t>Eddy Howard &amp; his Orchestra</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -5267,12 +5267,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>She Wore a Yellow Ribbon</t>
+          <t>Saturday Night Fish Fry (Parts I and II)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Andrews Sisters with Russ Morgan and his Orchestra</t>
+          <t>Louis Jordan &amp; His Tympany Five</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -5290,16 +5290,16 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Slaughter On Tenth Avenue</t>
+          <t>She Wore a Yellow Ribbon</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lennie Hayton Orchestra</t>
+          <t>Andrews Sisters with Russ Morgan and his Orchestra</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -5313,16 +5313,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sleigh Ride</t>
+          <t>Slaughter On Tenth Avenue</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Boston Pops Orchestra (Arthor Fiedler)</t>
+          <t>Lennie Hayton Orchestra</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>So In Love</t>
+          <t>Sleigh Ride</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Boston Pops Orchestra (Arthor Fiedler)</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -5364,11 +5364,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Gordon MacRae</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -5387,11 +5387,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Patti Page</t>
+          <t>Gordon MacRae</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -5405,16 +5405,16 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>So Tired</t>
+          <t>So In Love</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Kay Starr</t>
+          <t>Patti Page</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Russ Morgan</t>
+          <t>Kay Starr</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -5451,16 +5451,16 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Some Enchanted Evening</t>
+          <t>So Tired</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Bing Crosby with John Scott Trotter Orchestra</t>
+          <t>Russ Morgan</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -5479,11 +5479,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ezio Pinza</t>
+          <t>Bing Crosby with John Scott Trotter Orchestra</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -5502,11 +5502,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Frank Sinatra</t>
+          <t>Ezio Pinza</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -5525,11 +5525,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Jo Stafford</t>
+          <t>Frank Sinatra</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -5543,16 +5543,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Someday</t>
+          <t>Some Enchanted Evening</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mills Brothers</t>
+          <t>Jo Stafford</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -5566,16 +5566,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Somehow</t>
+          <t>Someday</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Billy Eckstine</t>
+          <t>Mills Brothers</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -5589,16 +5589,16 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Somehow</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Frank Sinatra</t>
+          <t>Billy Eckstine</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -5617,11 +5617,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Jack Fulton</t>
+          <t>Frank Sinatra</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -5640,11 +5640,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Jack Smith with The Crew Chiefs</t>
+          <t>Jack Fulton</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ray McKinley</t>
+          <t>Jack Smith with The Crew Chiefs</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -5686,11 +5686,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Russ Morgan &amp; The Skylarks</t>
+          <t>Ray McKinley</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -5704,16 +5704,16 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sweet Georgia Brown</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Brother Bones and His Shadows</t>
+          <t>Russ Morgan &amp; The Skylarks</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -5727,16 +5727,16 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>That Lucky Old Sun</t>
+          <t>Sweet Georgia Brown</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Louis Armstrong</t>
+          <t>Brother Bones and His Shadows</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -5755,11 +5755,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Vaughn Monroe &amp; His Orchestra</t>
+          <t>Louis Armstrong</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -5773,16 +5773,16 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>The Four Winds And The Seven Seas</t>
+          <t>That Lucky Old Sun</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sammy Kaye with Tony Alamo</t>
+          <t>Vaughn Monroe &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -5796,16 +5796,16 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>The Four Winds and The Seven Seas</t>
+          <t>The Four Winds And The Seven Seas</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mel Tormé</t>
+          <t>Sammy Kaye with Tony Alamo</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -5824,11 +5824,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Vic Damone</t>
+          <t>Mel Tormé</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -5842,16 +5842,16 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>The Lord's Prayer</t>
+          <t>The Four Winds and The Seven Seas</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Vic Damone</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -5865,16 +5865,16 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>The Old Master Painter</t>
+          <t>The Lord's Prayer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dick Haymes</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -5893,11 +5893,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Frank Sinatra</t>
+          <t>Dick Haymes</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Phil Harris and His Orchestra</t>
+          <t>Frank Sinatra</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -5939,11 +5939,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Richard Hayes with Mitch Miller's Orchestra</t>
+          <t>Phil Harris and His Orchestra</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -5962,11 +5962,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Snooky Lanson</t>
+          <t>Richard Hayes with Mitch Miller's Orchestra</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -5980,12 +5980,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>The Pussy Cat Song</t>
+          <t>The Old Master Painter</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Joy Nichols &amp; Benny Lee</t>
+          <t>Snooky Lanson</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -6008,11 +6008,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Patty Andrews with Bing Crosby</t>
+          <t>Joy Nichols &amp; Benny Lee</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -6031,11 +6031,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Patty Andrews with Bing Crosby</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -6049,16 +6049,16 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>There's No Tomorrow</t>
+          <t>The Pussy Cat Song</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tony Martin</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -6072,16 +6072,16 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Toot Toot, Tootsie</t>
+          <t>There's No Tomorrow</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Art Mooney &amp; His Orchestra</t>
+          <t>Tony Martin</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -6095,16 +6095,16 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Twelfth Street Rag</t>
+          <t>Toot Toot, Tootsie</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pee Wee Hunt</t>
+          <t>Art Mooney &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -6118,12 +6118,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Twenty-Four Hours of Sunshine</t>
+          <t>Twelfth Street Rag</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Art Mooney and His Orchestra</t>
+          <t>Pee Wee Hunt</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -6141,12 +6141,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Until</t>
+          <t>Twenty-Four Hours of Sunshine</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Tommy Dorsey with Harry Prime &amp; The Clark Sisters</t>
+          <t>Art Mooney and His Orchestra</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -6164,16 +6164,16 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Way Back Home</t>
+          <t>Until</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Bing Crosby with Fred Warren and His Pennsylvanians</t>
+          <t>Tommy Dorsey with Harry Prime &amp; The Clark Sisters</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -6187,16 +6187,16 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Whispering Hope</t>
+          <t>Way Back Home</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Jo Stafford and Gordon MacRae</t>
+          <t>Bing Crosby with Fred Warren and His Pennsylvanians</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -6210,16 +6210,16 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>White Christmas</t>
+          <t>Whispering Hope</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Jo Stafford and Gordon MacRae</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -6256,16 +6256,16 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Whos Girl Are You?</t>
+          <t>White Christmas</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Blue Barron and His Orchestra</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -6279,16 +6279,16 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Why Was I Born</t>
+          <t>Whos Girl Are You?</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Vic Damone</t>
+          <t>Blue Barron and His Orchestra</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -6302,16 +6302,16 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>With My Eyes Wide Open</t>
+          <t>Why Was I Born</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Patti Page with Vic Schoen and his Orchestra</t>
+          <t>Vic Damone</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D197" t="n">
         <v>0</v>
@@ -6325,12 +6325,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ya Wanna Buy a Bunny?</t>
+          <t>With My Eyes Wide Open</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Spike Jones &amp; His City Slickers</t>
+          <t>Patti Page with Vic Schoen and his Orchestra</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -6348,16 +6348,16 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Yingle Bells</t>
+          <t>Ya Wanna Buy a Bunny?</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Yogi Yorgesson</t>
+          <t>Spike Jones &amp; His City Slickers</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
@@ -6371,16 +6371,16 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>You Were Only Fooling</t>
+          <t>Yingle Bells</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Blue Barron with Clyde Burke</t>
+          <t>Yogi Yorgesson</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
@@ -6399,11 +6399,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Ink Spots</t>
+          <t>Blue Barron with Clyde Burke</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Kay Starr</t>
+          <t>Ink Spots</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -6440,16 +6440,16 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>You're Breaking My Heart</t>
+          <t>You Were Only Fooling</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Buddy Clark</t>
+          <t>Kay Starr</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -6468,11 +6468,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Jan Garber and His Orchestra</t>
+          <t>Buddy Clark</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D204" t="n">
         <v>0</v>
@@ -6486,16 +6486,16 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>You're Breaking my Heart</t>
+          <t>You're Breaking My Heart</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ink Spots</t>
+          <t>Jan Garber and His Orchestra</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
         <v>0</v>
@@ -6509,16 +6509,16 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>You're So Understanding</t>
+          <t>You're Breaking my Heart</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Evelyn Knight with Four Hits and a Miss</t>
+          <t>Ink Spots</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D206" t="n">
         <v>0</v>
@@ -6532,16 +6532,16 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>You, You, You Are The One</t>
+          <t>You're So Understanding</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Russ Morgan</t>
+          <t>Evelyn Knight with Four Hits and a Miss</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D207" t="n">
         <v>0</v>
@@ -6555,16 +6555,16 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>You, You, You Are the One</t>
+          <t>You, You, You Are The One</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>The Ames Brothers</t>
+          <t>Russ Morgan</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D208" t="n">
         <v>0</v>
@@ -6583,11 +6583,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>The Three Suns</t>
+          <t>The Ames Brothers</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
@@ -6597,6 +6597,29 @@
         <v>0</v>
       </c>
       <c r="G209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>You, You, You Are the One</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>The Three Suns</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6609,7 +6632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7782,16 +7805,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Five O'Clock Whistle</t>
+          <t>Ferryboat Serenade (La Piccinina)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Marion Hutton</t>
+          <t>The Andrews Sisters</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -7805,16 +7828,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>G'bye Now</t>
+          <t>Five O'Clock Whistle</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Woody Herman &amp; His Orchestra</t>
+          <t>Glenn Miller &amp; His Orchestra with Marion Hutton</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -7828,12 +7851,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Goodbye, Dear, I'll be Back in a Year</t>
+          <t>G'bye Now</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Horace Heidt &amp; His Musical Knights with Ronnie Kemper &amp; Donna W</t>
+          <t>Woody Herman &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -7851,12 +7874,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High on a Windy Hill</t>
+          <t>Goodbye, Dear, I'll be Back in a Year</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
+          <t>Horace Heidt &amp; His Musical Knights with Ronnie Kemper &amp; Donna W</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -7879,11 +7902,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Will Bradley &amp; His Orchestra</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -7897,16 +7920,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>I Don't Want to set the World on Fire</t>
+          <t>High on a Windy Hill</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Ink Spots</t>
+          <t>Will Bradley &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -7925,11 +7948,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tommy Tucker &amp; His Orchestra with Amy Arnell &amp; The Voices 3</t>
+          <t>The Ink Spots</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -7943,16 +7966,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>I Hear a Rhapsody</t>
+          <t>I Don't Want to set the World on Fire</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Tommy Tucker &amp; His Orchestra with Amy Arnell &amp; The Voices 3</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -7966,12 +7989,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>I'll Be With You In Apple Blossom Time</t>
+          <t>I Hear a Rhapsody</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Guy Lombardo &amp; His Royal Canadians</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -7994,11 +8017,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Andrews Sisters</t>
+          <t>Guy Lombardo &amp; His Royal Canadians</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -8012,16 +8035,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Intermezzo</t>
+          <t>I'll Be With You In Apple Blossom Time</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charlie Spivak &amp; His Orchestra</t>
+          <t>The Andrews Sisters</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -8040,11 +8063,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Freddy Martin &amp; His Orchestra with Clyde Rogers</t>
+          <t>Charlie Spivak &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -8063,11 +8086,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wayne King &amp; His Orchestra</t>
+          <t>Freddy Martin &amp; His Orchestra with Clyde Rogers</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -8081,16 +8104,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>It All Comes Back to Me Now</t>
+          <t>Intermezzo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hal Kemp &amp; His Orchestra with Bob Allen</t>
+          <t>Wayne King &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -8104,16 +8127,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>It All Comes Back to Me Now</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Hal Kemp &amp; His Orchestra with Bob Allen</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -8132,11 +8155,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Helen O'Connell</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -8150,16 +8173,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jingle Bells</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Tex Beneke &amp; Ernie Caceras</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Helen O'Connell</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -8173,16 +8196,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Just a Little Bit South of North Carolina</t>
+          <t>Jingle Bells</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gene Krupa &amp; His Orchestra with Anita O'Day</t>
+          <t>Glenn Miller &amp; His Orchestra with Tex Beneke &amp; Ernie Caceras</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -8196,12 +8219,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lament to Love</t>
+          <t>Just a Little Bit South of North Carolina</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Makers with Dick Haymes</t>
+          <t>Gene Krupa &amp; His Orchestra with Anita O'Day</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -8219,12 +8242,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Let Me Off Uptown</t>
+          <t>Lament to Love</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gene Kruppa &amp; His Orchestra with Anita O'Day and Roy Eldridge</t>
+          <t>Harry James &amp; His Music Makers with Dick Haymes</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -8242,16 +8265,16 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Let's Get Away From It All (Parts 1 &amp; 2)</t>
+          <t>Let Me Off Uptown</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tommy Dorsey with The Pied Pipers &amp; Connie Haynes &amp; Frank Sinatra</t>
+          <t>Gene Kruppa &amp; His Orchestra with Anita O'Day and Roy Eldridge</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -8265,16 +8288,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Maria Elena</t>
+          <t>Let's Get Away From It All (Parts 1 &amp; 2)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tony Pastor &amp; His Orchestra with Dorsey Anderson</t>
+          <t>Tommy Dorsey with The Pied Pipers &amp; Connie Haynes &amp; Frank Sinatra</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -8288,12 +8311,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Music Makers</t>
+          <t>Maria Elena</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Makers</t>
+          <t>Tony Pastor &amp; His Orchestra with Dorsey Anderson</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8311,16 +8334,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>New San Antonio Rose</t>
+          <t>Music Makers</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bing Crosby &amp; Bob Crosby &amp; His Orchestra</t>
+          <t>Harry James &amp; His Music Makers</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -8334,16 +8357,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Only Forever</t>
+          <t>New San Antonio Rose</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bing Crosby &amp; John Scott Trotter &amp; His Orchestra</t>
+          <t>Bing Crosby &amp; Bob Crosby &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -8357,16 +8380,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Perfidia</t>
+          <t>Only Forever</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Xavier Cugat &amp; His Orchestra</t>
+          <t>Bing Crosby &amp; John Scott Trotter &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -8380,16 +8403,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Shepherd Serenade</t>
+          <t>Perfidia</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Xavier Cugat &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -8408,11 +8431,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Horace Heidt &amp; His Orchestra with Larry Cotton &amp; The Glee Club</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -8426,16 +8449,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Star Dust</t>
+          <t>Shepherd Serenade</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Artie Shaw &amp; His Orchestra</t>
+          <t>Horace Heidt &amp; His Orchestra with Larry Cotton &amp; The Glee Club</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -8449,16 +8472,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Summit Ridge Drive</t>
+          <t>Star Dust</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Artie Shaw &amp; The Gramercy Five</t>
+          <t>Artie Shaw &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -8472,16 +8495,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>The Band Played On</t>
+          <t>Summit Ridge Drive</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Guy Lombardo &amp; His Royal Canadians with Kenny Gardner</t>
+          <t>Artie Shaw &amp; The Gramercy Five</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -8495,16 +8518,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>The Boogie Woogie Piggy</t>
+          <t>The Band Played On</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Tex Beneke &amp; The Modernaires</t>
+          <t>Guy Lombardo &amp; His Royal Canadians with Kenny Gardner</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -8518,16 +8541,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>The Hut-Sut Song</t>
+          <t>The Boogie Woogie Piggy</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Four King Sisters</t>
+          <t>Glenn Miller &amp; His Orchestra with Tex Beneke &amp; The Modernaires</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -8541,12 +8564,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>The Hut-Sut Song (A Swedish Serenade)</t>
+          <t>The Hut-Sut Song</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The King Sisters with Alvino Rey &amp; His Orchestra</t>
+          <t>The Four King Sisters</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -8564,16 +8587,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>The Things I Love</t>
+          <t>The Hut-Sut Song (A Swedish Serenade)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
+          <t>The King Sisters with Alvino Rey &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -8587,16 +8610,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>The Wise Old Owl</t>
+          <t>The Things I Love</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Al Donahue &amp; His Orchestra with Dee Keating</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -8610,12 +8633,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>There I Go</t>
+          <t>The Wise Old Owl</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Vaughn Monroe &amp; His Orchestra</t>
+          <t>Al Donahue &amp; His Orchestra with Dee Keating</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -8638,11 +8661,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Will Bradley &amp; His Orchestra with Jimmy Valentine</t>
+          <t>Vaughn Monroe &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -8656,16 +8679,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>There'll be Some Changes Made</t>
+          <t>There I Go</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Benny Goodman &amp; His Orchestra with Louise Tobin</t>
+          <t>Will Bradley &amp; His Orchestra with Jimmy Valentine</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -8679,16 +8702,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>This is No Laughing Matter</t>
+          <t>There'll be Some Changes Made</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Charlie Spivak &amp; His Orchestra with Garry Stevens</t>
+          <t>Benny Goodman &amp; His Orchestra with Louise Tobin</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -8702,16 +8725,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Til Reveille</t>
+          <t>This is No Laughing Matter</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bing Crosby with Scott Trotter &amp; His Orchestra</t>
+          <t>Charlie Spivak &amp; His Orchestra with Garry Stevens</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -8730,11 +8753,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kay Kyser, Harry Babbitt, Ginny Sims, Jack Martin, Max W</t>
+          <t>Bing Crosby with Scott Trotter &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -8748,16 +8771,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Time Was (Duerme)</t>
+          <t>Til Reveille</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Helen O'Connell</t>
+          <t>Kay Kyser, Harry Babbitt, Ginny Sims, Jack Martin, Max W</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -8771,16 +8794,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tonight We Love</t>
+          <t>Time Was (Duerme)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tony Martin with David Rose &amp; His Orchestra</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Helen O'Connell</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -8794,16 +8817,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Two In Love</t>
+          <t>Tonight We Love</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra</t>
+          <t>Tony Martin with David Rose &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -8817,12 +8840,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Until Tomorrow</t>
+          <t>Two In Love</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sammy Kaye &amp; His Orchestra with The Kaydets</t>
+          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -8840,12 +8863,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>We Three (My Echo, My Shadow and Me)</t>
+          <t>Until Tomorrow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Ink Spots</t>
+          <t>Sammy Kaye &amp; His Orchestra with The Kaydets</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -8863,16 +8886,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Yes, Indeed</t>
+          <t>We Three (My Echo, My Shadow and Me)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tommy Dorsey &amp; His Orchestra with Jo Stafford &amp; Sy Oliver</t>
+          <t>The Ink Spots</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -8886,16 +8909,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Yes, My Darling Daughter</t>
+          <t>Yes, Indeed</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Tommy Dorsey &amp; His Orchestra with Jo Stafford &amp; Sy Oliver</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -8909,16 +8932,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>You Made Me Love You</t>
+          <t>Yes, My Darling Daughter</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Makers</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -8932,12 +8955,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>You Walk By</t>
+          <t>You Made Me Love You</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Eddie Duchin &amp; His Orchestra with Johnny Drake</t>
+          <t>Harry James &amp; His Music Makers</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -8955,16 +8978,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>You and I</t>
+          <t>You Walk By</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bing Crosby with Scott Trotter &amp; His Orchestra</t>
+          <t>Eddie Duchin &amp; His Orchestra with Johnny Drake</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -8983,11 +9006,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
+          <t>Bing Crosby with Scott Trotter &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -8997,6 +9020,29 @@
         <v>0</v>
       </c>
       <c r="G96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>You and I</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9009,7 +9055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10106,16 +10152,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2022-01-17 00:00:00</t>
+          <t>(There'll Be Bluebirds Over) The White Cliffs of Dover</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NaT</t>
+          <t>Kay Kyser &amp; His Orchestra with Harry Babbit &amp; The Glee Club</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -11578,12 +11624,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Top 20 of 1942</t>
+          <t>White Christmas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bing Crosby &amp; The Ken Darby Singers with John Scott Trotter</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -11601,12 +11647,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>White Christmas</t>
+          <t>Who Wouldn't Love You</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bing Crosby &amp; The Ken Darby Singers with John Scott Trotter</t>
+          <t>Kay Kyser &amp; His Orchestra with Harry Babbit &amp; Trudy Erwin</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -11624,16 +11670,16 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Who Wouldn't Love You</t>
+          <t>Why Don't You Do Right?</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kay Kyser &amp; His Orchestra with Harry Babbit &amp; Trudy Erwin</t>
+          <t>Benny Goodman and His Orchestra</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -11647,16 +11693,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Why Don't You Do Right?</t>
+          <t>You Made Me Love You</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Benny Goodman and His Orchestra</t>
+          <t>Harry James &amp; His Music Makers</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -11666,29 +11712,6 @@
         <v>0</v>
       </c>
       <c r="G107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>You Made Me Love You</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Harry James &amp; His Music Makers</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>3</v>
-      </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11701,7 +11724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13280,16 +13303,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>You'd Be So Nice to Come Home To</t>
+          <t>Why Don't You Do Right?</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Benny Goodman &amp; His Orchestra with Peggy Lee</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -13303,16 +13326,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>You'll Never Know</t>
+          <t>You'd Be So Nice to Come Home To</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Willie Kelly</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -13322,6 +13345,29 @@
         <v>0</v>
       </c>
       <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>You'll Never Know</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Willie Kelly</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13334,7 +13380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13532,54 +13578,54 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>My Heart Tells Me (Should I Believe My Heart)</t>
+          <t>Besame Mucho (Kiss Me Much)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Glen Gray &amp; The Casa Loma Orchestra with Eugenie Baird</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Kitty Kallen</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Weeks 1-8</t>
+          <t>Weeks 4-14</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weeks 3-7</t>
+          <t>Weeks 8-14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I Love You</t>
+          <t>My Heart Tells Me (Should I Believe My Heart)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Glen Gray &amp; The Casa Loma Orchestra with Eugenie Baird</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Weeks 1-7</t>
+          <t>Weeks 1-8</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -13594,255 +13640,259 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mairzy Doats</t>
+          <t>I Love You</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Merry Macs</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Weeks 2-7</t>
+          <t>Weeks 1-7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Weeks 3-7</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I'm Making Believe</t>
+          <t>Mairzy Doats</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Ink Spots &amp; Ella Fitzgerald</t>
+          <t>The Merry Macs</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Weeks 3-7</t>
+          <t>Weeks 2-7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Weeks 3-4</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Don't Fence Me In</t>
+          <t>I'm Making Believe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bing Crosby &amp; The Andrews Sisters with Vic Schoen &amp; His Orchestra</t>
+          <t>The Ink Spots &amp; Ella Fitzgerald</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Weeks 4-7</t>
+          <t>Weeks 3-7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Weeks 5-7</t>
+          <t>Weeks 3-4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Holiday for Strings</t>
+          <t>Don't Fence Me In</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>David Rose &amp; His Orchestra</t>
+          <t>Bing Crosby &amp; The Andrews Sisters with Vic Schoen &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Weeks 8-11</t>
+          <t>Weeks 4-7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Weeks 5-7</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paper Doll</t>
+          <t>Holiday for Strings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mills Brothers</t>
+          <t>David Rose &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Weeks 1-4</t>
+          <t>Weeks 8-11</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Weeks 1-2</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Trolley Song</t>
+          <t>Paper Doll</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Pied Pipers with Paul Weston &amp; His Orchestra</t>
+          <t>The Mills Brothers</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Weeks 1-2</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>It's Love, Love, Love</t>
+          <t>The Trolley Song</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guy Lombardo &amp; His Royal Canadians with Skip Nelson</t>
+          <t>The Pied Pipers with Paul Weston &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Weeks 1-3</t>
+          <t>Weeks 9-12</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Weeks 2-3</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shoo-Shoo-Shoo Baby</t>
+          <t>It's Love, Love, Love</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Andrews Sisters with Vic Schoen &amp; His Orchestra</t>
+          <t>Guy Lombardo &amp; His Royal Canadians with Skip Nelson</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Weeks 5-7</t>
+          <t>Weeks 1-3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Weeks 2-3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Fernando Valley</t>
+          <t>Shoo-Shoo-Shoo Baby</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>The Andrews Sisters with Vic Schoen &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Weeks 6-7</t>
+          <t>Weeks 5-7</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -13853,23 +13903,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dance with a Dolly (With a Hole in her Stockin')</t>
+          <t>San Fernando Valley</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Russ Morgan &amp; His Orchestra with Al Jennings</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Weeks 5-5</t>
+          <t>Weeks 6-7</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -13880,23 +13930,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G.I. Jive</t>
+          <t>Dance with a Dolly (With a Hole in her Stockin')</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Louis Jordan &amp; His Tympani Five</t>
+          <t>Russ Morgan &amp; His Orchestra with Al Jennings</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Weeks 10-10</t>
+          <t>Weeks 5-5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -13907,23 +13957,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Is You Is Or Is You Ain't (Ma' Baby)</t>
+          <t>G.I. Jive</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bing Crosby &amp; The Andrews Sisters with Vic Schoen &amp; His Orchestra</t>
+          <t>Louis Jordan &amp; His Tympani Five</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Weeks 6-6</t>
+          <t>Weeks 10-10</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -13934,23 +13984,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Long Ago (And Far Away)</t>
+          <t>Is You Is Or Is You Ain't (Ma' Baby)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dick Haymes &amp; Helen Forrest with Camarata &amp; His Orchestra</t>
+          <t>Bing Crosby &amp; The Andrews Sisters with Vic Schoen &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Weeks 2-2</t>
+          <t>Weeks 6-6</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -13961,16 +14011,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Star Eyes</t>
+          <t>Long Ago (And Far Away)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Kitty Kallen</t>
+          <t>Dick Haymes &amp; Helen Forrest with Camarata &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -13988,23 +14038,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Time Waits for No One</t>
+          <t>Star Eyes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Helen Forrest with Camarata &amp; His Orchestra</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Kitty Kallen</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Weeks 4-4</t>
+          <t>Weeks 2-2</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -14015,16 +14065,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Together</t>
+          <t>Time Waits for No One</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dick Haymes &amp; Helen Forrest with Victor Young &amp; His Orchestra</t>
+          <t>Helen Forrest with Camarata &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -14042,21 +14092,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amor</t>
+          <t>Together</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Andy Russell</t>
+          <t>Dick Haymes &amp; Helen Forrest with Victor Young &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Weeks 4-4</t>
+        </is>
+      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
@@ -14070,7 +14124,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bing Crosby with John Scott Trotter &amp; His Orchestra</t>
+          <t>Andy Russell</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -14088,16 +14142,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>And Her Tears Flowed Like Wine</t>
+          <t>Amor</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stan Kenton &amp; His Orchestra with Anita O'Day &amp; Band Ensemble</t>
+          <t>Bing Crosby with John Scott Trotter &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -14111,16 +14165,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Besame Mucho</t>
+          <t>And Her Tears Flowed Like Wine</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Andy Russell</t>
+          <t>Stan Kenton &amp; His Orchestra with Anita O'Day &amp; Band Ensemble</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -14134,16 +14188,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Blue Rain</t>
+          <t>Besame Mucho</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
+          <t>Andy Russell</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -14157,16 +14211,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boogie Woogie</t>
+          <t>Blue Rain</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tommy Dorsey &amp; His Orchestra</t>
+          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -14180,16 +14234,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cherry</t>
+          <t>Boogie Woogie</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Makers</t>
+          <t>Tommy Dorsey &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -14203,12 +14257,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dance with a Dolly (With a Hole in her Stockin')</t>
+          <t>Cherry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Evelyn Knight with Camarata &amp; His Orchestra</t>
+          <t>Harry James &amp; His Music Makers</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -14226,12 +14280,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Do Nothin' Till You Hear From Me</t>
+          <t>Dance with a Dolly (With a Hole in her Stockin')</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Duke Ellington &amp; His Orchestra</t>
+          <t>Evelyn Knight with Camarata &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -14254,7 +14308,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Stan Kenton &amp; Red Dorris</t>
+          <t>Duke Ellington &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -14277,7 +14331,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Woody Herman &amp; His Orchestra</t>
+          <t>Stan Kenton &amp; Red Dorris</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -14295,16 +14349,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Don't Sweetheart Me</t>
+          <t>Do Nothin' Till You Hear From Me</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lawrence Welk &amp; His Royal Canadians with Wayne March</t>
+          <t>Woody Herman &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -14318,16 +14372,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>G.I. Jive</t>
+          <t>Don't Sweetheart Me</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Johnny Mercer</t>
+          <t>Lawrence Welk &amp; His Royal Canadians with Wayne March</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -14341,12 +14395,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Good Night, Wherever You Are</t>
+          <t>G.I. Jive</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Russ Morgan</t>
+          <t>Johnny Mercer</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -14364,16 +14418,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>His Rocking Horse Ran Away</t>
+          <t>Good Night, Wherever You Are</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Betty Hutton with Paul Weston &amp; His Orchestra</t>
+          <t>Russ Morgan</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -14387,16 +14441,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>How Many Hearts Have You Broken?</t>
+          <t>His Rocking Horse Ran Away</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stan Kenton &amp; His Orchestra with Gene Howard</t>
+          <t>Betty Hutton with Paul Weston &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -14410,12 +14464,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>How Sweet Are You</t>
+          <t>How Many Hearts Have You Broken?</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kay Armen</t>
+          <t>Stan Kenton &amp; His Orchestra with Gene Howard</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -14433,16 +14487,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>I Couldn't Sleep a Wink Last Night</t>
+          <t>How Sweet Are You</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frank Sinatra &amp; The Bobby Tucker Singers with Axel Stardahl</t>
+          <t>Kay Armen</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -14456,16 +14510,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>I Dream of You (More Than You Dream I Do)</t>
+          <t>I Couldn't Sleep a Wink Last Night</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Andy Russell</t>
+          <t>Frank Sinatra &amp; The Bobby Tucker Singers with Axel Stardahl</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -14484,7 +14538,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tommy Dorsey &amp; His Orchestra with Freddie Stewart</t>
+          <t>Andy Russell</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -14502,12 +14556,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>I Love You</t>
+          <t>I Dream of You (More Than You Dream I Do)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Enric Madriguera &amp; His Orchestra with Bob Lido</t>
+          <t>Tommy Dorsey &amp; His Orchestra with Freddie Stewart</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -14530,11 +14584,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jo Stafford with Paul Weston &amp; His Orchestra</t>
+          <t>Enric Madriguera &amp; His Orchestra with Bob Lido</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -14548,16 +14602,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>I'll Be Seeing You</t>
+          <t>I Love You</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra</t>
+          <t>Jo Stafford with Paul Weston &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -14571,16 +14625,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>I'll Get By</t>
+          <t>I'll Be Seeing You</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Ink Spots</t>
+          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -14594,16 +14648,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>I'll Walk Alone</t>
+          <t>I'll Get By</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Martha Tilton</t>
+          <t>The Ink Spots</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -14622,11 +14676,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mary Martin with Camarita &amp; His Orchestra</t>
+          <t>Martha Tilton</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -14640,16 +14694,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Into Each Life Some Rain Must Fall</t>
+          <t>I'll Walk Alone</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Ink Spots &amp; Ella Fitzgerald</t>
+          <t>Mary Martin with Camarita &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -14663,16 +14717,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Is You Is Or Is You Ain't (Ma' Baby)</t>
+          <t>Into Each Life Some Rain Must Fall</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Louis Jordan &amp; His Tympani Five</t>
+          <t>The Ink Spots &amp; Ella Fitzgerald</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -14686,12 +14740,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>It Could Happen To You</t>
+          <t>Is You Is Or Is You Ain't (Ma' Baby)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jo Stafford with Paul Weston &amp; His Orchestra</t>
+          <t>Louis Jordan &amp; His Tympani Five</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -14709,12 +14763,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>It Had to be You</t>
+          <t>It Could Happen To You</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Artie Shaw</t>
+          <t>Jo Stafford with Paul Weston &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -14737,11 +14791,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Betty Hutton with Paul Weston &amp; His Orchestra</t>
+          <t>Artie Shaw</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -14760,11 +14814,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dick Haymes &amp; Helen Forrest with Victor Young &amp; His Orchestra</t>
+          <t>Betty Hutton with Paul Weston &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -14778,12 +14832,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>It's Love, Love, Love</t>
+          <t>It Had to be You</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Four King Sisters with Vocal Chorus</t>
+          <t>Dick Haymes &amp; Helen Forrest with Victor Young &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -14801,16 +14855,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Long Ago (And Far Away)</t>
+          <t>It's Love, Love, Love</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>The Four King Sisters with Vocal Chorus</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -14829,11 +14883,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jo Stafford with Paul Weston &amp; His Orchestra</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -14852,11 +14906,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Jo Stafford with Paul Weston &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -14870,12 +14924,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mairzy Doats</t>
+          <t>Long Ago (And Far Away)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Al Trace &amp; His Orchestra with Al Trace &amp; Red Maddox</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -14898,7 +14952,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Pied Pipers with Paul Weston &amp; His Orchestra</t>
+          <t>Al Trace &amp; His Orchestra with Al Trace &amp; Red Maddox</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -14916,12 +14970,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Milkman Keep Those Bottles Quiet</t>
+          <t>Mairzy Doats</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ella Mae Morse</t>
+          <t>The Pied Pipers with Paul Weston &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -14939,16 +14993,16 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>My Ideal</t>
+          <t>Milkman Keep Those Bottles Quiet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
+          <t>Ella Mae Morse</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -14962,16 +15016,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>My Shining Hour</t>
+          <t>My Ideal</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Glen Gray &amp; The Casa Loma Orchestra with Eugenie Baird</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -14985,16 +15039,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>No Love, No Nothin'</t>
+          <t>My Shining Hour</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ella Mae Morse</t>
+          <t>Glen Gray &amp; The Casa Loma Orchestra with Eugenie Baird</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -15008,12 +15062,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>People Will Say We're In Love</t>
+          <t>No Love, No Nothin'</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bing Crosby, Trudy Erwin &amp; The Sportsmen</t>
+          <t>Ella Mae Morse</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -15031,16 +15085,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Poinciana (Song Of The Tree)</t>
+          <t>People Will Say We're In Love</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Bing Crosby, Trudy Erwin &amp; The Sportsmen</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -15054,16 +15108,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Shoo-Shoo-Shoo Baby</t>
+          <t>Poinciana (Song Of The Tree)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ella Mae Morse</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -15077,16 +15131,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Speak Low</t>
+          <t>Shoo-Shoo-Shoo Baby</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Guy Lombardo &amp; His Royal Canadians with Billy Leach</t>
+          <t>Ella Mae Morse</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -15100,16 +15154,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Straighten Up and Fly Right</t>
+          <t>Speak Low</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>King Cole Trio</t>
+          <t>Guy Lombardo &amp; His Royal Canadians with Billy Leach</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -15123,16 +15177,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>The Trolley Song</t>
+          <t>Straighten Up and Fly Right</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Judy Garland</t>
+          <t>King Cole Trio</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -15151,11 +15205,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vaughn Monroe &amp; His Orchestra with Marilyn Duke</t>
+          <t>Judy Garland</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -15169,12 +15223,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>There Goes That Song Again</t>
+          <t>The Trolley Song</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Russ Morgan &amp; His Orchestra</t>
+          <t>Vaughn Monroe &amp; His Orchestra with Marilyn Duke</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -15192,16 +15246,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>They're Either Too Young or Too Old</t>
+          <t>There Goes That Song Again</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Kitty Kallen</t>
+          <t>Russ Morgan &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -15215,16 +15269,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Till Then</t>
+          <t>They're Either Too Young or Too Old</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mills Brothers</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Kitty Kallen</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -15238,16 +15292,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Too-Ra-Loo-Ra-Loo-Ral</t>
+          <t>Till Then</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bing Crosby with John Scott Trotter &amp; His Orchestra</t>
+          <t>Mills Brothers</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -15261,16 +15315,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>When They Ask About You</t>
+          <t>Too-Ra-Loo-Ra-Loo-Ral</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Kitty Kallen</t>
+          <t>Bing Crosby with John Scott Trotter &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -15284,16 +15338,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>White Christmas</t>
+          <t>When They Ask About You</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bing Crosby &amp; The Ken Darby Singers with John Scott Trotter</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Kitty Kallen</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -15312,7 +15366,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Frank Sinatra &amp; The Bobby Tucker Singers with Axel Stardahl</t>
+          <t>Bing Crosby &amp; The Ken Darby Singers with John Scott Trotter</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -15326,6 +15380,29 @@
         <v>0</v>
       </c>
       <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>White Christmas</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Frank Sinatra &amp; The Bobby Tucker Singers with Axel Stardahl</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15338,7 +15415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17715,11 +17792,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vaughn Monroe &amp; His Orchestra with Marilyn Duke</t>
+          <t>The Pied Pipers with Paul Weston &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -17733,16 +17810,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>There Goes That Song Again</t>
+          <t>The Trolley Song</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kay Kyser &amp; His Orchestra with Gerogia Carroll</t>
+          <t>Vaughn Monroe &amp; His Orchestra with Marilyn Duke</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -17761,11 +17838,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Russ Morgan &amp; His Orchestra</t>
+          <t>Kay Kyser &amp; His Orchestra with Gerogia Carroll</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -17784,11 +17861,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sammy Kaye &amp; His Orchestra with Nancy Norman</t>
+          <t>Russ Morgan &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -17802,12 +17879,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Waitin' for the Train to Come In</t>
+          <t>There Goes That Song Again</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Orchestra</t>
+          <t>Sammy Kaye &amp; His Orchestra with Nancy Norman</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -17830,11 +17907,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Peggy Lee</t>
+          <t>Harry James &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -17848,16 +17925,16 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>White Christmas</t>
+          <t>Waitin' for the Train to Come In</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bing Crosby &amp; The Ken Darby Singers with John Scott Trotter</t>
+          <t>Peggy Lee</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -17871,16 +17948,16 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Who Threw the Whisky in the Well?</t>
+          <t>White Christmas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lucky Millinder</t>
+          <t>Bing Crosby &amp; The Ken Darby Singers with John Scott Trotter</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -17894,16 +17971,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>You Belong to My Heart</t>
+          <t>Who Threw the Whisky in the Well?</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bing Crosby with Xavier Cugat &amp; His Orchestra</t>
+          <t>Lucky Millinder</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -17922,11 +17999,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Charlie Spivak &amp; His Orchestra</t>
+          <t>Bing Crosby with Xavier Cugat &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -17936,6 +18013,29 @@
         <v>0</v>
       </c>
       <c r="G106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>You Belong to My Heart</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Charlie Spivak &amp; His Orchestra</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17948,7 +18048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19727,16 +19827,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>The Christmas Song</t>
+          <t>Symphony</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>King Cole Trio</t>
+          <t>Jo Stafford</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -19750,12 +19850,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>The Coffee Song</t>
+          <t>The Christmas Song</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Frank Sinatra</t>
+          <t>King Cole Trio</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -19773,16 +19873,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>The Gypsy</t>
+          <t>The Coffee Song</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sammy Kaye with Mary Marlow</t>
+          <t>Frank Sinatra</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -19796,16 +19896,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>The Old Lamplighter</t>
+          <t>The Gypsy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hal Derwin</t>
+          <t>Sammy Kaye with Mary Marlow</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -19819,16 +19919,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>They Say It's Wonderful</t>
+          <t>The Old Lamplighter</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Frank Sinatra</t>
+          <t>Hal Derwin</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -19847,11 +19947,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Frank Sinatra</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -19865,16 +19965,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>To Each His Own</t>
+          <t>They Say It's Wonderful</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Modernaires with Paula Kelly</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -19893,11 +19993,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tony Martin</t>
+          <t>The Modernaires with Paula Kelly</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -19911,16 +20011,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>White Christmas</t>
+          <t>To Each His Own</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frank Sinatra &amp; The Bobby Tucker Singers with Axel Stardahl</t>
+          <t>Tony Martin</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -19934,12 +20034,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Winter Wonderland</t>
+          <t>White Christmas</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Frank Sinatra &amp; The Bobby Tucker Singers with Axel Stardahl</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -19957,16 +20057,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>You Won't Be Satisfied</t>
+          <t>Winter Wonderland</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Les Brown with Doris Day</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -19976,6 +20076,29 @@
         <v>0</v>
       </c>
       <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>You Won't Be Satisfied</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Les Brown with Doris Day</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19988,7 +20111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21912,16 +22035,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Open the Door Richard</t>
+          <t>Ole Buttermilk Sky</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jack McVea</t>
+          <t>Paul Weston with Matt Dennis</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -21940,7 +22063,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Louis Jordan</t>
+          <t>Jack McVea</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -21963,11 +22086,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Three Flames</t>
+          <t>Louis Jordan</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -21981,16 +22104,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Peg O' My Heart</t>
+          <t>Open the Door Richard</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Art Lund</t>
+          <t>Three Flames</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -22009,11 +22132,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Buddy Clark</t>
+          <t>Art Lund</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -22032,11 +22155,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Clark Dennis</t>
+          <t>Buddy Clark</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -22050,12 +22173,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Rumours Are Flying</t>
+          <t>Peg O' My Heart</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Frankie Carle with Marjorie Hughes</t>
+          <t>Clark Dennis</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -22073,16 +22196,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Serenade of the Bells</t>
+          <t>Rumours Are Flying</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jo Stafford</t>
+          <t>Frankie Carle with Marjorie Hughes</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -22101,11 +22224,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kay Kyser</t>
+          <t>Jo Stafford</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -22124,11 +22247,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sammy Kaye with Don Cornell &amp; The Kaydets</t>
+          <t>Kay Kyser</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -22142,16 +22265,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Smoke! Smoke! Smoke (That Cigarette)</t>
+          <t>Serenade of the Bells</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Phil Harris</t>
+          <t>Sammy Kaye with Don Cornell &amp; The Kaydets</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -22165,16 +22288,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sugar Blues</t>
+          <t>Smoke! Smoke! Smoke (That Cigarette)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ted Weems and His Orchestra</t>
+          <t>Phil Harris</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -22188,16 +22311,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>That's My Desire</t>
+          <t>Sugar Blues</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Frankie Laine</t>
+          <t>Ted Weems and His Orchestra</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -22211,16 +22334,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>The Old Lamplighter</t>
+          <t>That's My Desire</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Hal Derwin</t>
+          <t>Frankie Laine</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -22239,11 +22362,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Kay Kyser with Michael Douglas</t>
+          <t>Hal Derwin</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -22257,12 +22380,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>The Whiffenpoof Song</t>
+          <t>The Old Lamplighter</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bing Crosby with The Fred Waring Glee Club</t>
+          <t>Kay Kyser with Michael Douglas</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -22280,16 +22403,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>White Christmas</t>
+          <t>The Whiffenpoof Song</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Bing Crosby with The Fred Waring Glee Club</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -22303,16 +22426,16 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>You Do</t>
+          <t>White Christmas</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bing Crosby with Carmen Cavallaro</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -22331,11 +22454,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Bing Crosby with Carmen Cavallaro</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -22354,11 +22477,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Margaret Whiting</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -22377,11 +22500,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vaughn Monroe</t>
+          <t>Margaret Whiting</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -22391,6 +22514,29 @@
         <v>0</v>
       </c>
       <c r="G97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>You Do</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Vaughn Monroe</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>7</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22403,7 +22549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24936,12 +25082,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Now is the Hour</t>
+          <t>Near You</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Charlie Spivak with Tommy Mercer</t>
+          <t>Larry Green Trio</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -24964,11 +25110,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Eddy Howard</t>
+          <t>Charlie Spivak with Tommy Mercer</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -24987,11 +25133,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Gracie Fields</t>
+          <t>Eddy Howard</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -25010,11 +25156,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Margaret Whiting</t>
+          <t>Gracie Fields</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -25028,16 +25174,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>On A Slow Boat To China</t>
+          <t>Now is the Hour</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Art Lund</t>
+          <t>Margaret Whiting</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -25056,11 +25202,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Benny Goodman with Al Hendrickson</t>
+          <t>Art Lund</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -25079,11 +25225,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eddy Howard</t>
+          <t>Benny Goodman with Al Hendrickson</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -25102,11 +25248,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Freddy Martin with Glenn Hughes</t>
+          <t>Eddy Howard</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -25125,11 +25271,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Larry Clinton</t>
+          <t>Freddy Martin with Glenn Hughes</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -25143,12 +25289,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Powder Your Face With Sunshine</t>
+          <t>On A Slow Boat To China</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Evelyn Knight with The Stardusters</t>
+          <t>Larry Clinton</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -25166,12 +25312,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Rambling Rose</t>
+          <t>Powder Your Face With Sunshine</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Gordon MacRae and The Starlighters</t>
+          <t>Evelyn Knight with The Stardusters</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -25194,11 +25340,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Gordon MacRae and The Starlighters</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -25212,16 +25358,16 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Run, Joe</t>
+          <t>Rambling Rose</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Louis Jordan &amp; His Tympany 5</t>
+          <t>Perry Como</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -25235,16 +25381,16 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sabre Dance</t>
+          <t>Run, Joe</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Woody Herman</t>
+          <t>Louis Jordan &amp; His Tympany 5</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -25258,16 +25404,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sabre Dance Boogie</t>
+          <t>Sabre Dance</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Freddy Martin with Barclay Allen</t>
+          <t>Woody Herman</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -25281,16 +25427,16 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Say Something Sweet To Your Sweetheart</t>
+          <t>Sabre Dance Boogie</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Jo Stafford &amp; Gordon MacRae and the Starlighters</t>
+          <t>Freddy Martin with Barclay Allen</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -25304,16 +25450,16 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Serenade of the Bells</t>
+          <t>Say Something Sweet To Your Sweetheart</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Jo Stafford</t>
+          <t>Jo Stafford &amp; Gordon MacRae and the Starlighters</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -25327,16 +25473,16 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Serutan Yob</t>
+          <t>Serenade of the Bells</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>The Unusual Seven</t>
+          <t>Jo Stafford</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -25350,16 +25496,16 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Shine</t>
+          <t>Serutan Yob</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Frankie Laine</t>
+          <t>The Unusual Seven</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -25373,16 +25519,16 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Slap 'er Down Agin, Paw</t>
+          <t>Shine</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Arthur Godfrey</t>
+          <t>Frankie Laine</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -25396,16 +25542,16 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>So Tired</t>
+          <t>Slap 'er Down Agin, Paw</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Russ Morgan</t>
+          <t>Arthur Godfrey</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -25419,16 +25565,16 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>St. Louis Blues March</t>
+          <t>So Tired</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tex Beneke</t>
+          <t>Russ Morgan</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -25442,16 +25588,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sweet Georgia Brown</t>
+          <t>St. Louis Blues March</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Brother Bones and His Shadows</t>
+          <t>Tex Beneke</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -25465,16 +25611,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tea Leaves</t>
+          <t>Sweet Georgia Brown</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Emile Cote's Serenaders</t>
+          <t>Brother Bones and His Shadows</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -25493,7 +25639,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jack Smith with The Clark Sisters</t>
+          <t>Emile Cote's Serenaders</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -25511,16 +25657,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tell Me a Story</t>
+          <t>Tea Leaves</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Sammy Kaye with Don Cornell &amp; The Kaydets</t>
+          <t>Jack Smith with The Clark Sisters</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -25534,16 +25680,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>That Certain Party</t>
+          <t>Tell Me a Story</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Benny Strong</t>
+          <t>Sammy Kaye with Don Cornell &amp; The Kaydets</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -25557,16 +25703,16 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>The Dickey-Bird Song</t>
+          <t>That Certain Party</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Freddy Martin with Glenn Hughes</t>
+          <t>Benny Strong</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -25585,11 +25731,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Larry Clinton</t>
+          <t>Freddy Martin with Glenn Hughes</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -25603,16 +25749,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>The Maharajah Of Magador</t>
+          <t>The Dickey-Bird Song</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Vaughn Monroe with Ziggy Talent</t>
+          <t>Larry Clinton</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -25626,16 +25772,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Toolie Oolie Doolie (The Yodel Polka)</t>
+          <t>The Maharajah Of Magador</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Andrews Sisters</t>
+          <t>Vaughn Monroe with Ziggy Talent</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -25654,11 +25800,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Henri Rene and The Musette Orchestra</t>
+          <t>Andrews Sisters</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -25677,7 +25823,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>The Martin Sisters</t>
+          <t>Henri Rene and The Musette Orchestra</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -25700,11 +25846,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>The Sportsmen</t>
+          <t>The Martin Sisters</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -25723,11 +25869,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vaughn Horton with The Polka Debs</t>
+          <t>The Sportsmen</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -25741,16 +25887,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Underneath The Arches</t>
+          <t>Toolie Oolie Doolie (The Yodel Polka)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Andrews Sisters</t>
+          <t>Vaughn Horton with The Polka Debs</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -25769,11 +25915,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Andy Russell and The Pied Pipers</t>
+          <t>Andrews Sisters</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -25792,11 +25938,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Primo Scala Banjo and Accordion Orchestra</t>
+          <t>Andy Russell and The Pied Pipers</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -25815,11 +25961,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ray McKinley</t>
+          <t>Primo Scala Banjo and Accordion Orchestra</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -25833,16 +25979,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Until</t>
+          <t>Underneath The Arches</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tommy Dorsey with Harry Prime &amp; The Clark Sisters</t>
+          <t>Ray McKinley</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -25856,16 +26002,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>White Christmas</t>
+          <t>Until</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Tommy Dorsey with Harry Prime &amp; The Clark Sisters</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -25879,16 +26025,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>William Tell Overture (Feedlebaum)</t>
+          <t>White Christmas</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Spike Jones &amp; His City Slickers with Doodles Weaver</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -25902,16 +26048,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Woody Woodpecker</t>
+          <t>William Tell Overture (Feedlebaum)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>The Andrews Sisters with Danny Kaye</t>
+          <t>Spike Jones &amp; His City Slickers with Doodles Weaver</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -25925,16 +26071,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>You Call Everybody Darlin'</t>
+          <t>Woody Woodpecker</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Andrews Sisters</t>
+          <t>The Andrews Sisters with Danny Kaye</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -25953,11 +26099,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Anne Vincent</t>
+          <t>Andrews Sisters</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -25976,11 +26122,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Jack Lathrop and the Drugstore Cowboys</t>
+          <t>Anne Vincent</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -25999,11 +26145,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Jack Smith with The Clark Sisters</t>
+          <t>Jack Lathrop and the Drugstore Cowboys</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -26022,11 +26168,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Jerry Wayne</t>
+          <t>Jack Smith with The Clark Sisters</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -26040,16 +26186,16 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>You Came a Long Way</t>
+          <t>You Call Everybody Darlin'</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ray McKinley</t>
+          <t>Jerry Wayne</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -26063,16 +26209,16 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>You Can't Be True Dear</t>
+          <t>You Came a Long Way</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dick Haymes with The Song Spinners</t>
+          <t>Ray McKinley</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -26091,11 +26237,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dick James</t>
+          <t>Dick Haymes with The Song Spinners</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -26114,7 +26260,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Marlin Sisters with Eddie Fisher</t>
+          <t>Dick James</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -26137,11 +26283,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>The Sportsmen</t>
+          <t>Marlin Sisters with Eddie Fisher</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -26160,11 +26306,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Vera Lynn</t>
+          <t>The Sportsmen</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -26178,16 +26324,16 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>You Do</t>
+          <t>You Can't Be True Dear</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Bing Crosby with Carmen Cavallaro</t>
+          <t>Vera Lynn</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -26201,16 +26347,16 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>You Were Only Foolin'</t>
+          <t>You Do</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Blue Barron with Clyde Burke</t>
+          <t>Bing Crosby with Carmen Cavallaro</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -26229,11 +26375,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Kay Starr</t>
+          <t>Blue Barron with Clyde Burke</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -26247,16 +26393,16 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>You Were Only Fooling</t>
+          <t>You Were Only Foolin'</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ink Spots</t>
+          <t>Kay Starr</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -26270,16 +26416,16 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>You're All I Want for Christmas</t>
+          <t>You Were Only Fooling</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Frankie Laine</t>
+          <t>Ink Spots</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -26289,6 +26435,29 @@
         <v>0</v>
       </c>
       <c r="G162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>You're All I Want for Christmas</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Frankie Laine</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>3</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tasks/finalpool/music-analysis/groundtruth_workspace/music_analysis_result.xlsx
+++ b/tasks/finalpool/music-analysis/groundtruth_workspace/music_analysis_result.xlsx
@@ -9055,7 +9055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9701,54 +9701,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Blues in the Night</t>
+          <t>Deep in the Heart of Texas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Woody Herman &amp; His Orchestra</t>
+          <t>Alvino Rey &amp; His Orchestra with Bill Schallen &amp; Skeets Herfurt</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Weeks 2-2</t>
+          <t>Weeks 3-3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Weeks 2-2</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deep in the Heart of Texas</t>
+          <t>Der Fuehrer's Face</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alvino Rey &amp; His Orchestra with Bill Schallen &amp; Skeets Herfurt</t>
+          <t>Spike Jones &amp; His City Slickers with Carl Grayson</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Weeks 3-3</t>
+          <t>Weeks 4-4</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -9759,23 +9755,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Der Fuehrer's Face</t>
+          <t>I Had the Craziest Dream</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spike Jones &amp; His City Slickers with Carl Grayson</t>
+          <t>Harry James &amp; His Music Makers with Hellen Forrest</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Weeks 4-4</t>
+          <t>Weeks 6-6</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -9786,23 +9782,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Der Fuehrer's Face</t>
+          <t>I Left My Heart at the Stage Door Canteen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spike Jones &amp; His City Slickers with Carl Grayson</t>
+          <t>Sammy Kaye &amp; His Orchestra with Don Cornell</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Weeks 2-2</t>
+          <t>Weeks 3-3</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -9813,23 +9809,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I Had the Craziest Dream</t>
+          <t>I Said No!</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Makers with Hellen Forrest</t>
+          <t>Alvino Rey &amp; His Orchestra with Yvonne King</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Weeks 6-6</t>
+          <t>Weeks 4-4</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -9840,23 +9836,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>I Left My Heart at the Stage Door Canteen</t>
+          <t>Just as Though You Were Here</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sammy Kaye &amp; His Orchestra with Don Cornell</t>
+          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra and The Pied Pipers</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Weeks 3-3</t>
+          <t>Weeks 8-8</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -9867,16 +9863,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>I Said No!</t>
+          <t>Mister Five by Five</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alvino Rey &amp; His Orchestra with Yvonne King</t>
+          <t>Harry James &amp; His Music Makers with Hellen Forrest</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -9894,23 +9890,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>I Said No!</t>
+          <t>Piano Concerto in B Flat</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alvino Rey &amp; His Orchestra with Yvonne King</t>
+          <t>Freddy Martin &amp; His Orchestra with Jack Fina</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Weeks 2-2</t>
+          <t>Weeks 1-1</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -9921,23 +9917,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Just as Though You Were Here</t>
+          <t>Remember Pearl Harbor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra and The Pied Pipers</t>
+          <t>Sammy Kaye &amp; His Orchestra with The Glee Club</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Weeks 8-8</t>
+          <t>Weeks 3-3</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -9948,23 +9944,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mister Five by Five</t>
+          <t>When the Lights Go On Again (All Over the World)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Makers with Hellen Forrest</t>
+          <t>Vaughn Monroe &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Weeks 4-4</t>
+          <t>Weeks 7-7</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -9975,25 +9971,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Piano Concerto in B Flat</t>
+          <t>(There'll Be Bluebirds Over) The White Cliffs of Dover</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Freddy Martin &amp; His Orchestra with Jack Fina</t>
+          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Weeks 1-1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
         <v>0</v>
       </c>
@@ -10002,25 +9994,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Remember Pearl Harbor</t>
+          <t>(There'll Be Bluebirds Over) The White Cliffs of Dover</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sammy Kaye &amp; His Orchestra with The Glee Club</t>
+          <t>Kate Smith</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Weeks 3-3</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
         <v>0</v>
       </c>
@@ -10029,25 +10017,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Serenade in Blue</t>
+          <t>(There'll Be Bluebirds Over) The White Cliffs of Dover</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle &amp; The Modernaires</t>
+          <t>Kay Kyser &amp; His Orchestra with Harry Babbit &amp; The Glee Club</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Weeks 2-2</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
         <v>0</v>
       </c>
@@ -10056,25 +10040,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>When the Lights Go On Again (All Over the World)</t>
+          <t>A Zoot Suit</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vaughn Monroe &amp; His Orchestra</t>
+          <t>Kay Kyser &amp; His Orchestra with Sully Mason &amp; Trudy Erwin</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Weeks 7-7</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>0</v>
       </c>
@@ -10083,16 +10063,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>(I've Got a Gal In) Kalamazoo</t>
+          <t>Always on my Heart</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Marion Hutton &amp; Tex Beneke</t>
+          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -10106,16 +10086,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>(There'll Be Bluebirds Over) The White Cliffs of Dover</t>
+          <t>Amen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
+          <t>Abe Lyman &amp; His Orchestra &amp; Chorus with Rose Blane</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -10129,16 +10109,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>(There'll Be Bluebirds Over) The White Cliffs of Dover</t>
+          <t>Amen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kate Smith</t>
+          <t>Woody Herman &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -10152,12 +10132,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>(There'll Be Bluebirds Over) The White Cliffs of Dover</t>
+          <t>Blues in the Night</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kay Kyser &amp; His Orchestra with Harry Babbit &amp; The Glee Club</t>
+          <t>Cab Calloway</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -10175,16 +10155,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A String of Pearls</t>
+          <t>Blues in the Night</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -10198,16 +10178,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A Zoot Suit</t>
+          <t>Blues in the Night</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kay Kyser &amp; His Orchestra with Sully Mason &amp; Trudy Erwin</t>
+          <t>Jimmy Lunceford &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -10221,16 +10201,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Always on my Heart</t>
+          <t>Cow-Cow Boogie</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
+          <t>Freddie Slack &amp; His Orchestra with Ella Mae Morse</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -10244,12 +10224,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Amen</t>
+          <t>Daybreak</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Abe Lyman &amp; His Orchestra &amp; Chorus with Rose Blane</t>
+          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -10267,16 +10247,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Amen</t>
+          <t>Dearly Beloved</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Woody Herman &amp; His Orchestra</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -10290,16 +10270,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Blues in the Night</t>
+          <t>Dearly Beloved</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cab Calloway</t>
+          <t>Glenn Miller &amp; His Orchestra with Skip Nelson</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -10313,16 +10293,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Blues in the Night</t>
+          <t>Deep in the Heart of Texas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Horace Heidt &amp; His Musical Knights</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -10336,16 +10316,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Blues in the Night</t>
+          <t>Everything I Love</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jimmy Lunceford &amp; His Orchestra</t>
+          <t>Glenn Miller &amp; His Orchestra with Ray Eberle &amp; Chorus</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -10359,16 +10339,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Chatanooga Choo Choo</t>
+          <t>He's My Guy</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Tex Beneke &amp; The Modernaires</t>
+          <t>Harry James &amp; His Music Makers with Hellen Forrest</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -10382,16 +10362,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cow-Cow Boogie</t>
+          <t>I Don't Want to Talk Without You</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Freddie Slack &amp; His Orchestra with Ella Mae Morse</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -10405,12 +10385,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Daybreak</t>
+          <t>I Left My Heart at the Stage Door Canteen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra</t>
+          <t>Charlie Spivak &amp; His Orchestra with Garry Stevens</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -10428,12 +10408,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dearly Beloved</t>
+          <t>I Remember You</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -10451,16 +10431,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dearly Beloved</t>
+          <t>I Said No</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Skip Nelson</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Helen O'Connell</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -10474,12 +10454,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Deep in the Heart of Texas</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Horace Heidt &amp; His Musical Knights</t>
+          <t>Benny Goodman &amp; His Orchestra with Dick Haymes</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -10497,16 +10477,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Don't Sit Under the Apple Tree</t>
+          <t>Jersey Bounce</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Marion Hutton &amp; Tex Beneke</t>
+          <t>Jimmy Dorsey &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -10520,16 +10500,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Everything I Love</t>
+          <t>Jingle, Jangle, Jingle</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle &amp; Chorus</t>
+          <t>The Merry Macs</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -10543,16 +10523,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>He Wears a Pair of Silver Wings</t>
+          <t>Johnny Doughboy Found a Rose in Ireland</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kay Kyser &amp; His Orchestra with Harry Babbitt</t>
+          <t>Guy Lombardo &amp; His Royal Canadians with Kenny Gardner</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -10566,12 +10546,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>He's My Guy</t>
+          <t>Johnny Doughboy Found a Rose in Ireland</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Makers with Hellen Forrest</t>
+          <t>Kay Kyser &amp; His Orchestra with The Glee Cliub</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -10589,16 +10569,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>I Don't Want to Talk Without You</t>
+          <t>Juke Box Saturday Night</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Glenn Miller &amp; His Orchestra with Tex Beneke &amp; Marion Hutton</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -10612,7 +10592,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>I Don't Want to Walk Without You</t>
+          <t>Manhattan Serenade</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10621,7 +10601,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -10635,12 +10615,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>I Left My Heart at the Stage Door Canteen</t>
+          <t>Miss You</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charlie Spivak &amp; His Orchestra with Garry Stevens</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -10658,16 +10638,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>I Remember You</t>
+          <t>Miss You</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -10681,12 +10661,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>I Said No</t>
+          <t>Mister Five by Five</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Helen O'Connell</t>
+          <t>Freddie Slack &amp; His Orchestra with Ella Mae Morse</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -10704,16 +10684,16 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Moonlight Becomes You</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Benny Goodman &amp; His Orchestra with Dick Haymes</t>
+          <t>Glenn Miller &amp; His Orchestra with Skip Nelson &amp; The Modernaires</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -10727,16 +10707,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Jersey Bounce</t>
+          <t>My Devotion</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Benny Goodman &amp; His Orchestra</t>
+          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -10750,16 +10730,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jersey Bounce</t>
+          <t>My Devotion</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra</t>
+          <t>Vaughn Monroe &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -10773,16 +10753,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jingle, Jangle, Jingle</t>
+          <t>One Dozen Roses</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kay Kyser &amp; His Orchestra with Harry Babbitt &amp; Julie Conway</t>
+          <t>Dinah Shore</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -10796,16 +10776,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jingle, Jangle, Jingle</t>
+          <t>One Dozen Roses</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Merry Macs</t>
+          <t>Glen Gray &amp; The Casa Loma Orchestra with Pee Wee Hunt</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -10819,16 +10799,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Johnny Doughboy Found a Rose in Ireland</t>
+          <t>One Dozen Roses</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Guy Lombardo &amp; His Royal Canadians with Kenny Gardner</t>
+          <t>Harry James &amp; His Music Masters with Jimmy Saunders</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -10842,16 +10822,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Johnny Doughboy Found a Rose in Ireland</t>
+          <t>Praise the Lord and Pass the Ammunition</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kay Kyser &amp; His Orchestra with The Glee Cliub</t>
+          <t>The Merry Macs</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -10865,16 +10845,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Juke Box Saturday Night</t>
+          <t>Rosie O'Day (The Filla-Ga-Dusha Song)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Tex Beneke &amp; Marion Hutton</t>
+          <t>Kate Smith</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -10888,16 +10868,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Manhattan Serenade</t>
+          <t>Shepherd Serenade</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Makers with Hellen Forrest</t>
+          <t>Bing Crosby</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -10911,16 +10891,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Miss You</t>
+          <t>Skylark</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bing Crosby</t>
+          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -10934,16 +10914,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Miss You</t>
+          <t>Somebody Else Is Taking My Place</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Benny Goodman &amp; His Orchestra with Peggy Lee</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -10957,16 +10937,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mister Five by Five</t>
+          <t>Somebody Else Is Taking My Place</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Freddie Slack &amp; His Orchestra with Ella Mae Morse</t>
+          <t>Russ Morgan &amp; His Orchestra with The Morganaires</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -10980,16 +10960,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Moonlight Becomes You</t>
+          <t>Strictly Instrumental</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Skip Nelson &amp; The Modernaires</t>
+          <t>Harry James &amp; His Music Makers</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -11003,16 +10983,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Moonlight Cocktail</t>
+          <t>Strip Polka</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle &amp; The Modernaires</t>
+          <t>Alvino Rey &amp; His Orchestra &amp; His Chorus with The Four King Sisters</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -11026,16 +11006,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>My Devotion</t>
+          <t>Strip Polka</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Charlie Spivak &amp; His Orchestra with Garry Stevens</t>
+          <t>Johnny Mercer &amp; The Mellowaires</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -11049,16 +11029,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>My Devotion</t>
+          <t>Strip Polka</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly</t>
+          <t>Kay Kyser &amp; His Orchestra with Jack Martin &amp; The Glee Club</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -11072,16 +11052,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>My Devotion</t>
+          <t>Strip Polka</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Vaughn Monroe &amp; His Orchestra</t>
+          <t>The Andrews Sister</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -11095,16 +11075,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>One Dozen Roses</t>
+          <t>Sweet Eloise</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dinah Shore</t>
+          <t>Glenn Miller &amp; His Orchestra with Ray Eberle &amp; The Modernaires</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -11118,16 +11098,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>One Dozen Roses</t>
+          <t>Take Me</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Glen Gray &amp; The Casa Loma Orchestra with Pee Wee Hunt</t>
+          <t>Benny Goodman &amp; His Orchestra with Dick Haymes</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -11141,16 +11121,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>One Dozen Roses</t>
+          <t>Take Me</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Masters with Jimmy Saunders</t>
+          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -11164,16 +11144,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>One Dozen Roses</t>
+          <t>This is No Laughing Matter</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Harry James &amp; His Music Masters with Jimmy Saunders</t>
+          <t>Charlie Spivak &amp; His Orchestra with Garry Stevens</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -11187,16 +11167,16 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Praise the Lord and Pass the Ammunition</t>
+          <t>Tonight We Love</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kay Kyser &amp; His Orchestra with The Glee Cliub</t>
+          <t>Tony Martin with David Rose &amp; His Orchestra</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -11210,16 +11190,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Praise the Lord and Pass the Ammunition</t>
+          <t>Why Don't You Do Right?</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Merry Macs</t>
+          <t>Benny Goodman and His Orchestra</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -11233,12 +11213,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Rosie O'Day (The Filla-Ga-Dusha Song)</t>
+          <t>You Made Me Love You</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kate Smith</t>
+          <t>Harry James &amp; His Music Makers</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -11252,466 +11232,6 @@
         <v>0</v>
       </c>
       <c r="G87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Shepherd Serenade</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Bing Crosby</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>2</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Skylark</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>11</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Sleepy Lagoon</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Harry James &amp; His Music Makers</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Somebody Else Is Taking My Place</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Benny Goodman &amp; His Orchestra with Peggy Lee</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>9</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Somebody Else Is Taking My Place</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Russ Morgan &amp; His Orchestra with The Morganaires</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>6</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Strictly Instrumental</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Harry James &amp; His Music Makers</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>4</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Strip Polka</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Alvino Rey &amp; His Orchestra &amp; His Chorus with The Four King Sisters</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>2</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Strip Polka</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Johnny Mercer &amp; The Mellowaires</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>3</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Strip Polka</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Kay Kyser &amp; His Orchestra with Jack Martin &amp; The Glee Club</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>2</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Strip Polka</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>The Andrews Sister</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>4</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Sweet Eloise</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Glenn Miller &amp; His Orchestra with Ray Eberle &amp; The Modernaires</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>3</v>
-      </c>
-      <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Take Me</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Benny Goodman &amp; His Orchestra with Dick Haymes</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Take Me</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Tommy Dorsey &amp; His Orchestra with Frank Sinatra</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>3</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Tangerine</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Jimmy Dorsey &amp; His Orchestra with Bob Eberly &amp; Helen O'Connell</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>This is No Laughing Matter</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Charlie Spivak &amp; His Orchestra with Garry Stevens</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Tonight We Love</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Tony Martin with David Rose &amp; His Orchestra</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>White Christmas</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Bing Crosby &amp; The Ken Darby Singers with John Scott Trotter</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Who Wouldn't Love You</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Kay Kyser &amp; His Orchestra with Harry Babbit &amp; Trudy Erwin</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Why Don't You Do Right?</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Benny Goodman and His Orchestra</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>You Made Me Love You</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Harry James &amp; His Music Makers</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>3</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
